--- a/naver-place-crawler/results_nail/울산_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/울산_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>미용교육</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>뮤토 헤어&amp;네일</t>
+          <t>뷰티엠네일학원</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bongbong323@naver.com</t>
+          <t>mneilacademy@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>070-4322-1500</t>
+          <t>0507-1441-6677</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>울산 남구 대학로84번길 9 1층</t>
+          <t>울산 중구 화합로 301 2층 1호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muto_hair</t>
+          <t>https://imaginary-game-952mnailacademy.notion.site/237cc200dc1d80e7acc2f35102296974?pvs=143</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wfefiw1</t>
+          <t>https://talk.naver.com/ct/w887jmk</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>111</v>
+        <v>5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="R2" t="n">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2029027701</t>
+          <t>2034629521</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2029027701</t>
+          <t>https://m.place.naver.com/place/2034629521</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2829</v>
+        <v>2873</v>
       </c>
       <c r="Q3" t="n">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="R3" t="n">
-        <v>3284</v>
+        <v>3348</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>route12796@naver.com</t>
+          <t>obvious8923@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -858,34 +858,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>레푸스 울산삼산점</t>
+          <t>몰젠</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>tnqo11@naver.com</t>
+          <t>lover77lovet@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1318-6022</t>
+          <t>0507-1324-6649</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>울산 남구 신정로126번길 50 3층</t>
+          <t>울산 중구 명륜로 69 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_duIaT</t>
+          <t>https://www.instagram.com/morgen.kr</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -900,13 +900,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4x0uy</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -915,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>360</v>
+        <v>688</v>
       </c>
       <c r="Q5" t="n">
-        <v>611</v>
+        <v>180</v>
       </c>
       <c r="R5" t="n">
-        <v>971</v>
+        <v>868</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1902831178</t>
+          <t>1061557985</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1902831178</t>
+          <t>https://m.place.naver.com/place/1061557985</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -952,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>몰젠</t>
+          <t>코하네일 울산달동점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>klchr@naver.com</t>
+          <t>zlsel007@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1324-6649</t>
+          <t>0507-1480-0540</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>울산 중구 명륜로 69 2층</t>
+          <t>울산 남구 삼산로199번길 44 2층 202호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/morgen.kr</t>
+          <t>https://www.instagram.com/koha_nail_/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -999,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4x0uy</t>
+          <t>https://talk.naver.com/ct/wqkf7h7</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>686</v>
+        <v>201</v>
       </c>
       <c r="Q6" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="R6" t="n">
-        <v>864</v>
+        <v>377</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1061557985</t>
+          <t>1431771374</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1061557985</t>
+          <t>https://m.place.naver.com/place/1431771374</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1050,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>네일오브유</t>
+          <t>네일더끌림</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nailofyou@naver.com</t>
+          <t>jko0197@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1348-1025</t>
+          <t>0507-1449-5053</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>울산 남구 삼산중로 88 3층</t>
+          <t>울산 남구 화합로 198 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailofyou</t>
+          <t>http://www.instagram.com/cclim1160</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,12 +1101,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcfz53</t>
+          <t>https://talk.naver.com/ct/wc6kke</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1111,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1785</v>
+        <v>1824</v>
       </c>
       <c r="Q7" t="n">
-        <v>260</v>
+        <v>167</v>
       </c>
       <c r="R7" t="n">
-        <v>2045</v>
+        <v>1991</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1544421180</t>
+          <t>1418359883</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1544421180</t>
+          <t>https://m.place.naver.com/place/1418359883</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1209,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q8" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="R8" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1234,7 +1238,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1307,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Q9" t="n">
         <v>56</v>
       </c>
       <c r="R9" t="n">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1332,7 +1336,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1344,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일,라비</t>
+          <t>하이푸스 울산수암점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>minjang08@naver.com</t>
+          <t>balck789@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1406-0436</t>
+          <t>0507-1326-6497</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>울산 남구 중앙로 21 3층</t>
+          <t>울산 남구 수암로90번길 15 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail__ravi</t>
+          <t>https://www.instagram.com/hifuss_ulsansuam/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1386,10 +1390,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yhi3</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1401,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="Q10" t="n">
-        <v>40</v>
+        <v>234</v>
       </c>
       <c r="R10" t="n">
-        <v>60</v>
+        <v>269</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,17 +1424,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2037973254</t>
+          <t>1721842914</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037973254</t>
+          <t>https://m.place.naver.com/place/1721842914</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1438,34 +1446,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>늘네일</t>
+          <t>힌이네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>song92pq@naver.com</t>
+          <t>harin5131@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>052-285-7715</t>
+          <t>0507-1408-1768</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>울산 북구 신기14길 2 1층 103호</t>
+          <t>울산 중구 남외2길 25 어반캐슬 2차 104호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_neul.nail?igsh=MWY3eG9zNGk3cWZvcw==</t>
+          <t>http://pf.kakao.com/_YDDhX/chat</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1485,12 +1493,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w44ab4</t>
+          <t>https://talk.naver.com/ct/w9dt58x</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1499,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>326</v>
+        <v>71</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R11" t="n">
-        <v>331</v>
+        <v>81</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,17 +1522,213 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1465990109</t>
+          <t>2057349909</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1465990109</t>
+          <t>https://m.place.naver.com/place/2057349909</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>뭉네일</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>hisuging@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1370-7720</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>울산 북구 신기16길 3 1층 뭉네일</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_GXxjAX/chat</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wn54j8e</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>17</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2091569869</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2091569869</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>여니디데이</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>soi4005@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1315-1965</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>울산 동구 방어진순환도로 652 D동 107-2호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yeoni.d_day?igsh=aTJkMjE1dmxjbmho</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wu1crc4</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>10</v>
+      </c>
+      <c r="R13" t="n">
+        <v>16</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2063002293</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2063002293</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/울산_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/울산_네일샵.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>네일아트,네일샵</t>
+          <t>미용교육</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>봄날뷰티디자인</t>
+          <t>뷰티엠네일학원</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>luv0e@naver.com</t>
+          <t>mneilacademy@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1330-3351</t>
+          <t>0507-1441-6677</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>울산 남구 화합로 185 업스퀘어 지하1층 B115호</t>
+          <t>울산 중구 화합로 301 2층 1호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/luv0e</t>
+          <t>https://imaginary-game-952mnailacademy.notion.site/237cc200dc1d80e7acc2f35102296974?pvs=143</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcekds</t>
+          <t>https://talk.naver.com/ct/w887jmk</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1440</v>
+        <v>5</v>
       </c>
       <c r="Q2" t="n">
-        <v>588</v>
+        <v>60</v>
       </c>
       <c r="R2" t="n">
-        <v>2028</v>
+        <v>65</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>84861537</t>
+          <t>2034629521</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/84861537</t>
+          <t>https://m.place.naver.com/place/2034629521</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cold39882@naver.com</t>
+          <t>wet7873@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>이끌림뷰티 울산신정점</t>
+          <t>네일오브유</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ecclim_beauty@naver.com</t>
+          <t>nailofyou@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1312-2437</t>
+          <t>0507-1348-1025</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>울산 남구 월평로 135 2층 이끌림뷰티</t>
+          <t>울산 남구 삼산중로 88 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ecclim_beauty</t>
+          <t>http://instagram.com/nailofyou</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4wl81</t>
+          <t>https://talk.naver.com/ct/wcfz53</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>863</v>
+        <v>1809</v>
       </c>
       <c r="Q7" t="n">
-        <v>549</v>
+        <v>294</v>
       </c>
       <c r="R7" t="n">
-        <v>1412</v>
+        <v>2103</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1106985438</t>
+          <t>1544421180</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1106985438</t>
+          <t>https://m.place.naver.com/place/1544421180</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1216,10 +1216,10 @@
         <v>68</v>
       </c>
       <c r="Q8" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="R8" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>하이푸스 울산수암점</t>
+          <t>엔피케어 울산중구점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>balck789@naver.com</t>
+          <t>np_care@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1326-6497</t>
+          <t>0507-1349-7661</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>울산 남구 수암로90번길 15 3층</t>
+          <t>울산 중구 종가6길 4-5 7층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hifuss_ulsansuam/</t>
+          <t>https://blog.naver.com/np_care</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5yhi3</t>
+          <t>https://talk.naver.com/ct/w493pt</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>35</v>
+        <v>476</v>
       </c>
       <c r="Q9" t="n">
-        <v>234</v>
+        <v>56</v>
       </c>
       <c r="R9" t="n">
-        <v>269</v>
+        <v>532</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1721842914</t>
+          <t>1654457357</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1721842914</t>
+          <t>https://m.place.naver.com/place/1654457357</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1348,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일굿데이</t>
+          <t>하이푸스 울산수암점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kockok@naver.com</t>
+          <t>balck789@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1355-8034</t>
+          <t>0507-1326-6497</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>울산 남구 수암로 138 118호</t>
+          <t>울산 남구 수암로90번길 15 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_good_day?igsh=OXFnZGpncnRnZ24w</t>
+          <t>https://www.instagram.com/hifuss_ulsansuam/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ghe0a</t>
+          <t>https://talk.naver.com/ct/w5yhi3</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>475</v>
+        <v>35</v>
       </c>
       <c r="Q10" t="n">
-        <v>17</v>
+        <v>234</v>
       </c>
       <c r="R10" t="n">
-        <v>492</v>
+        <v>269</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1540860319</t>
+          <t>1721842914</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1540860319</t>
+          <t>https://m.place.naver.com/place/1721842914</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1446,25 +1446,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>예다움</t>
+          <t>오트스튜디오네일 울산삼산점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>enrms22@naver.com</t>
+          <t>gnwns1800@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1413-4969</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>울산 남구 삼산중로74번길 22 301호 예다움</t>
+          <t>울산 남구 삼산로 120 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/yedaum.nailstudio</t>
+          <t>https://blog.naver.com/gnwns1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1479,7 +1483,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1489,7 +1493,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcs1xf</t>
+          <t>https://talk.naver.com/ct/w5zyve</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>191</v>
+        <v>131</v>
       </c>
       <c r="Q11" t="n">
-        <v>702</v>
+        <v>46</v>
       </c>
       <c r="R11" t="n">
-        <v>893</v>
+        <v>177</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,12 +1522,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1563881738</t>
+          <t>1148014599</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1563881738</t>
+          <t>https://m.place.naver.com/place/1148014599</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_nail/울산_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/울산_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,8 +426,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="49" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,44 +559,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>미용교육</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>뷰티엠네일학원</t>
+          <t>봄날뷰티디자인</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mneilacademy@naver.com</t>
+          <t>luv0e@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1441-6677</t>
+          <t>0507-1330-3351</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>울산 중구 화합로 301 2층 1호</t>
+          <t>울산 남구 화합로 185 업스퀘어 지하1층 B115호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://imaginary-game-952mnailacademy.notion.site/237cc200dc1d80e7acc2f35102296974?pvs=143</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w887jmk</t>
+          <t>https://talk.naver.com/ct/wcekds</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>5</v>
+        <v>1440</v>
       </c>
       <c r="Q2" t="n">
-        <v>60</v>
+        <v>588</v>
       </c>
       <c r="R2" t="n">
-        <v>65</v>
+        <v>2028</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2034629521</t>
+          <t>84861537</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2034629521</t>
+          <t>https://m.place.naver.com/place/84861537</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_about.j2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2889</v>
+        <v>2892</v>
       </c>
       <c r="Q3" t="n">
         <v>480</v>
       </c>
       <c r="R3" t="n">
-        <v>3369</v>
+        <v>3372</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/koha_nail_/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -861,11 +861,7 @@
           <t>몰젠</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>lover77lovet@naver.com</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
@@ -880,7 +876,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/morgen.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,7 +886,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -944,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -978,7 +974,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_fromj/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,7 +984,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1017,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="Q6" t="n">
         <v>293</v>
       </c>
       <c r="R6" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1042,7 +1038,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1072,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://instagram.com/nailofyou</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,7 +1082,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1115,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1809</v>
+        <v>1815</v>
       </c>
       <c r="Q7" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="R7" t="n">
-        <v>2103</v>
+        <v>2111</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1140,7 +1136,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1234,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1268,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/np_care</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1282,12 +1278,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1336,7 +1332,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1366,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hifuss_ulsansuam/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1380,7 +1376,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1412,10 +1408,10 @@
         <v>35</v>
       </c>
       <c r="Q10" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="R10" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1434,7 +1430,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1464,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gnwns1800</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1478,12 +1474,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1532,7 +1528,105 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>네일앤디디</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>nailndd@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1363-4443</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>울산 남구 번영로 195 동문아뮤티 상가 1층 109호 네일앤디디</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcel28</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>31</v>
+      </c>
+      <c r="R12" t="n">
+        <v>164</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1432858320</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1432858320</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
